--- a/GradeSession_1_Dec/1/student/hoangbsthe186345/GradeSummary.xlsx
+++ b/GradeSession_1_Dec/1/student/hoangbsthe186345/GradeSummary.xlsx
@@ -40,13 +40,13 @@
     <x:t>Message</x:t>
   </x:si>
   <x:si>
-    <x:t>Passed 3/4 test cases</x:t>
+    <x:t>Passed 1/4 test cases</x:t>
   </x:si>
   <x:si>
     <x:t>Start Time</x:t>
   </x:si>
   <x:si>
-    <x:t>2025-12-01 01:19:58</x:t>
+    <x:t>2025-12-01 03:16:52</x:t>
   </x:si>
   <x:si>
     <x:t>End Time</x:t>
@@ -424,7 +424,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">

--- a/GradeSession_1_Dec/1/student/hoangbsthe186345/GradeSummary.xlsx
+++ b/GradeSession_1_Dec/1/student/hoangbsthe186345/GradeSummary.xlsx
@@ -46,7 +46,7 @@
     <x:t>Start Time</x:t>
   </x:si>
   <x:si>
-    <x:t>2025-12-01 03:16:52</x:t>
+    <x:t>2025-12-01 10:02:32</x:t>
   </x:si>
   <x:si>
     <x:t>End Time</x:t>
